--- a/xls/square_high_un_16_tri3_23.xlsx
+++ b/xls/square_high_un_16_tri3_23.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>741</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>340</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>598</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>3330</v>
+      </c>
+      <c r="I21">
+        <v>-1.8467607534160728</v>
+      </c>
+      <c r="J21">
+        <v>-1.5233774413186898</v>
+      </c>
+      <c r="K21">
+        <v>1.0506339585701185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>741</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>340</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>668</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>3738</v>
+      </c>
+      <c r="I22">
+        <v>-0.501601946896271</v>
+      </c>
+      <c r="J22">
+        <v>-0.429388752166519</v>
+      </c>
+      <c r="K22">
+        <v>2.53814270200007</v>
+      </c>
+    </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>11</v>
